--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123091148</v>
+        <v>123091145</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57629</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,20 +931,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,14 +954,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123091145</v>
+        <v>123091148</v>
       </c>
       <c r="B5" t="n">
-        <v>57629</v>
+        <v>57848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,20 +1055,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,14 +1078,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123091142</v>
+        <v>123091150</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>58156</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,16 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -799,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123091150</v>
+        <v>123091148</v>
       </c>
       <c r="B3" t="n">
-        <v>58156</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +811,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,7 +835,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123091145</v>
+        <v>123091142</v>
       </c>
       <c r="B4" t="n">
-        <v>57629</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,16 +935,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -961,7 +961,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123091148</v>
+        <v>123091145</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
+        <v>57629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,20 +1055,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,14 +1078,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123091150</v>
+        <v>123091148</v>
       </c>
       <c r="B2" t="n">
-        <v>58156</v>
+        <v>57848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +715,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -795,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123091148</v>
+        <v>123091145</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57629</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,14 +834,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -919,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123091142</v>
+        <v>123091150</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>58156</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,20 +935,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,16 +958,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123091145</v>
+        <v>123091142</v>
       </c>
       <c r="B5" t="n">
-        <v>57629</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123091148</v>
+        <v>123091142</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123091145</v>
+        <v>123091150</v>
       </c>
       <c r="B3" t="n">
-        <v>57629</v>
+        <v>58156</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,16 +834,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -923,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123091150</v>
+        <v>123091148</v>
       </c>
       <c r="B4" t="n">
-        <v>58156</v>
+        <v>57848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,16 +935,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,7 +959,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123091142</v>
+        <v>123091145</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57629</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123091142</v>
+        <v>123091150</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>58159</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,16 +710,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -799,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123091150</v>
+        <v>123091145</v>
       </c>
       <c r="B3" t="n">
-        <v>58156</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +807,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,12 +830,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>123091148</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123091145</v>
+        <v>123091142</v>
       </c>
       <c r="B5" t="n">
-        <v>57629</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1164,6 +1164,732 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123432412</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57851</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skåneleden, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>410583</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6239538</v>
+      </c>
+      <c r="S6" t="n">
+        <v>45</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123445750</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fäje myr norr, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>410535</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6239462</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123445753</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fäje myr norr, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>410586</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6239506</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123429666</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57851</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skåneleden, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>410584</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6239531</v>
+      </c>
+      <c r="S9" t="n">
+        <v>54</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123432410</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skåneleden, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>410583</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6239538</v>
+      </c>
+      <c r="S10" t="n">
+        <v>45</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123445749</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fäje myr norr, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>410567</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6239439</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123091150</v>
+        <v>123091142</v>
       </c>
       <c r="B2" t="n">
-        <v>58159</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,12 +710,16 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -795,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123091145</v>
+        <v>123091150</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
+        <v>58159</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,16 +834,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123091142</v>
+        <v>123091145</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>57632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1167,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123432412</v>
+        <v>123445749</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,20 +1179,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1202,30 +1202,34 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410583</v>
+        <v>410567</v>
       </c>
       <c r="R6" t="n">
-        <v>6239538</v>
+        <v>6239439</v>
       </c>
       <c r="S6" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,19 +1256,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,22 +1273,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123445750</v>
+        <v>123429666</v>
       </c>
       <c r="B7" t="n">
-        <v>57632</v>
+        <v>57851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,20 +1297,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1329,31 +1323,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410535</v>
+        <v>410584</v>
       </c>
       <c r="R7" t="n">
-        <v>6239462</v>
+        <v>6239531</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1380,9 +1370,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,22 +1397,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123445753</v>
+        <v>123432412</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
+        <v>57851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1421,20 +1421,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1444,34 +1444,30 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410586</v>
+        <v>410583</v>
       </c>
       <c r="R8" t="n">
-        <v>6239506</v>
+        <v>6239538</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,9 +1494,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,22 +1521,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123429666</v>
+        <v>123445753</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>57632</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,20 +1545,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1565,27 +1571,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410584</v>
+        <v>410586</v>
       </c>
       <c r="R9" t="n">
-        <v>6239531</v>
+        <v>6239506</v>
       </c>
       <c r="S9" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1612,19 +1622,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,12 +1639,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123445749</v>
+        <v>123445750</v>
       </c>
       <c r="B11" t="n">
         <v>57632</v>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410567</v>
+        <v>410535</v>
       </c>
       <c r="R11" t="n">
-        <v>6239439</v>
+        <v>6239462</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -1167,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123445749</v>
+        <v>123429666</v>
       </c>
       <c r="B6" t="n">
-        <v>57632</v>
+        <v>57851</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,20 +1179,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1205,31 +1205,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410567</v>
+        <v>410584</v>
       </c>
       <c r="R6" t="n">
-        <v>6239439</v>
+        <v>6239531</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,9 +1252,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,22 +1279,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123429666</v>
+        <v>123445749</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>57632</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,20 +1303,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1323,27 +1329,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410584</v>
+        <v>410567</v>
       </c>
       <c r="R7" t="n">
-        <v>6239531</v>
+        <v>6239439</v>
       </c>
       <c r="S7" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1370,19 +1380,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,12 +1397,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -1167,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123429666</v>
+        <v>123445749</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,20 +1179,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1205,27 +1205,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410584</v>
+        <v>410567</v>
       </c>
       <c r="R6" t="n">
-        <v>6239531</v>
+        <v>6239439</v>
       </c>
       <c r="S6" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,19 +1256,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,19 +1273,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123445749</v>
+        <v>123432410</v>
       </c>
       <c r="B7" t="n">
         <v>57632</v>
@@ -1329,31 +1323,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410567</v>
+        <v>410583</v>
       </c>
       <c r="R7" t="n">
-        <v>6239439</v>
+        <v>6239538</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1380,9 +1370,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,19 +1397,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123432412</v>
+        <v>123429666</v>
       </c>
       <c r="B8" t="n">
         <v>57851</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1461,13 +1461,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410583</v>
+        <v>410584</v>
       </c>
       <c r="R8" t="n">
-        <v>6239538</v>
+        <v>6239531</v>
       </c>
       <c r="S8" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1533,7 +1533,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123445753</v>
+        <v>123445750</v>
       </c>
       <c r="B9" t="n">
         <v>57632</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410586</v>
+        <v>410535</v>
       </c>
       <c r="R9" t="n">
-        <v>6239506</v>
+        <v>6239462</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123432410</v>
+        <v>123432412</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
+        <v>57851</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1663,20 +1663,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,7 +1775,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123445750</v>
+        <v>123445753</v>
       </c>
       <c r="B11" t="n">
         <v>57632</v>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410535</v>
+        <v>410586</v>
       </c>
       <c r="R11" t="n">
-        <v>6239462</v>
+        <v>6239506</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123091150</v>
+        <v>123091142</v>
       </c>
       <c r="B2" t="n">
-        <v>58159</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,12 +710,16 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -795,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123091145</v>
+        <v>123091148</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
+        <v>57857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,14 +834,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -919,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123091142</v>
+        <v>123091145</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57638</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,16 +939,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -961,7 +965,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1043,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123091148</v>
+        <v>123091150</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>58165</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,16 +1063,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1083,11 +1087,7 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123429666</v>
+        <v>123432410</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57638</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,20 +1179,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1209,7 +1209,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410584</v>
+        <v>410583</v>
       </c>
       <c r="R6" t="n">
-        <v>6239531</v>
+        <v>6239538</v>
       </c>
       <c r="S6" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,7 +1294,7 @@
         <v>123432412</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123432410</v>
+        <v>123429666</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
+        <v>57857</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,20 +1427,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1457,7 +1457,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410583</v>
+        <v>410584</v>
       </c>
       <c r="R8" t="n">
-        <v>6239538</v>
+        <v>6239531</v>
       </c>
       <c r="S8" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123445749</v>
+        <v>123445750</v>
       </c>
       <c r="B9" t="n">
-        <v>57632</v>
+        <v>57638</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410567</v>
+        <v>410535</v>
       </c>
       <c r="R9" t="n">
-        <v>6239439</v>
+        <v>6239462</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1660,7 +1660,7 @@
         <v>123445753</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
+        <v>57638</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123445750</v>
+        <v>123445749</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
+        <v>57638</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410535</v>
+        <v>410567</v>
       </c>
       <c r="R11" t="n">
-        <v>6239462</v>
+        <v>6239439</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123445753</v>
+        <v>123445749</v>
       </c>
       <c r="B10" t="n">
         <v>57638</v>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410586</v>
+        <v>410567</v>
       </c>
       <c r="R10" t="n">
-        <v>6239506</v>
+        <v>6239439</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123445749</v>
+        <v>123445753</v>
       </c>
       <c r="B11" t="n">
         <v>57638</v>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410567</v>
+        <v>410586</v>
       </c>
       <c r="R11" t="n">
-        <v>6239439</v>
+        <v>6239506</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123091142</v>
+        <v>123091145</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>57641</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123091148</v>
+        <v>123091150</v>
       </c>
       <c r="B3" t="n">
-        <v>57857</v>
+        <v>58168</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,11 +839,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -923,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123091145</v>
+        <v>123091148</v>
       </c>
       <c r="B4" t="n">
-        <v>57638</v>
+        <v>57860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,20 +931,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,14 +954,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1047,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123091150</v>
+        <v>123091142</v>
       </c>
       <c r="B5" t="n">
-        <v>58165</v>
+        <v>57506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,20 +1055,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,12 +1078,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123432410</v>
+        <v>123429666</v>
       </c>
       <c r="B6" t="n">
-        <v>57638</v>
+        <v>57860</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,20 +1179,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1209,7 +1209,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410583</v>
+        <v>410584</v>
       </c>
       <c r="R6" t="n">
-        <v>6239538</v>
+        <v>6239531</v>
       </c>
       <c r="S6" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,7 +1294,7 @@
         <v>123432412</v>
       </c>
       <c r="B7" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123429666</v>
+        <v>123445753</v>
       </c>
       <c r="B8" t="n">
-        <v>57857</v>
+        <v>57641</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,20 +1427,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1453,27 +1453,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410584</v>
+        <v>410586</v>
       </c>
       <c r="R8" t="n">
-        <v>6239531</v>
+        <v>6239506</v>
       </c>
       <c r="S8" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1500,19 +1504,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,22 +1521,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123445750</v>
+        <v>123445749</v>
       </c>
       <c r="B9" t="n">
-        <v>57638</v>
+        <v>57641</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1595,10 +1589,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410535</v>
+        <v>410567</v>
       </c>
       <c r="R9" t="n">
-        <v>6239462</v>
+        <v>6239439</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1657,10 +1651,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123445749</v>
+        <v>123432410</v>
       </c>
       <c r="B10" t="n">
-        <v>57638</v>
+        <v>57641</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1695,31 +1689,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410567</v>
+        <v>410583</v>
       </c>
       <c r="R10" t="n">
-        <v>6239439</v>
+        <v>6239538</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1746,9 +1736,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,22 +1763,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123445753</v>
+        <v>123445750</v>
       </c>
       <c r="B11" t="n">
-        <v>57638</v>
+        <v>57641</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410586</v>
+        <v>410535</v>
       </c>
       <c r="R11" t="n">
-        <v>6239506</v>
+        <v>6239462</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123091145</v>
       </c>
       <c r="B2" t="n">
-        <v>57641</v>
+        <v>57642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123091150</v>
+        <v>123091142</v>
       </c>
       <c r="B3" t="n">
-        <v>58168</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,12 +834,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -922,7 +926,7 @@
         <v>123091148</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1043,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123091142</v>
+        <v>123091150</v>
       </c>
       <c r="B5" t="n">
-        <v>57506</v>
+        <v>58169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,20 +1059,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,16 +1082,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>123429666</v>
       </c>
       <c r="B6" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>123432412</v>
       </c>
       <c r="B7" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123445753</v>
+        <v>123445750</v>
       </c>
       <c r="B8" t="n">
-        <v>57641</v>
+        <v>57642</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410586</v>
+        <v>410535</v>
       </c>
       <c r="R8" t="n">
-        <v>6239506</v>
+        <v>6239462</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123445749</v>
+        <v>123432410</v>
       </c>
       <c r="B9" t="n">
-        <v>57641</v>
+        <v>57642</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1571,31 +1571,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410567</v>
+        <v>410583</v>
       </c>
       <c r="R9" t="n">
-        <v>6239439</v>
+        <v>6239538</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1622,9 +1618,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,22 +1645,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123432410</v>
+        <v>123445753</v>
       </c>
       <c r="B10" t="n">
-        <v>57641</v>
+        <v>57642</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,27 +1695,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410583</v>
+        <v>410586</v>
       </c>
       <c r="R10" t="n">
-        <v>6239538</v>
+        <v>6239506</v>
       </c>
       <c r="S10" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1736,19 +1746,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,22 +1763,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123445750</v>
+        <v>123445749</v>
       </c>
       <c r="B11" t="n">
-        <v>57641</v>
+        <v>57642</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410535</v>
+        <v>410567</v>
       </c>
       <c r="R11" t="n">
-        <v>6239462</v>
+        <v>6239439</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123429666</v>
+        <v>123432412</v>
       </c>
       <c r="B6" t="n">
         <v>57861</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410584</v>
+        <v>410583</v>
       </c>
       <c r="R6" t="n">
-        <v>6239531</v>
+        <v>6239538</v>
       </c>
       <c r="S6" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,10 +1291,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123432412</v>
+        <v>123445749</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>57642</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,20 +1303,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1326,30 +1326,34 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410583</v>
+        <v>410567</v>
       </c>
       <c r="R7" t="n">
-        <v>6239538</v>
+        <v>6239439</v>
       </c>
       <c r="S7" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,19 +1380,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,19 +1397,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123445750</v>
+        <v>123432410</v>
       </c>
       <c r="B8" t="n">
         <v>57642</v>
@@ -1453,31 +1447,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410535</v>
+        <v>410583</v>
       </c>
       <c r="R8" t="n">
-        <v>6239462</v>
+        <v>6239538</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1504,9 +1494,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,22 +1521,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123432410</v>
+        <v>123429666</v>
       </c>
       <c r="B9" t="n">
-        <v>57642</v>
+        <v>57861</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1575,7 +1575,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1585,13 +1585,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410583</v>
+        <v>410584</v>
       </c>
       <c r="R9" t="n">
-        <v>6239538</v>
+        <v>6239531</v>
       </c>
       <c r="S9" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,7 +1657,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123445753</v>
+        <v>123445750</v>
       </c>
       <c r="B10" t="n">
         <v>57642</v>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410586</v>
+        <v>410535</v>
       </c>
       <c r="R10" t="n">
-        <v>6239506</v>
+        <v>6239462</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123445749</v>
+        <v>123445753</v>
       </c>
       <c r="B11" t="n">
         <v>57642</v>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410567</v>
+        <v>410586</v>
       </c>
       <c r="R11" t="n">
-        <v>6239439</v>
+        <v>6239506</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -1167,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123432412</v>
+        <v>123445749</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>57642</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,20 +1179,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1202,30 +1202,34 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410583</v>
+        <v>410567</v>
       </c>
       <c r="R6" t="n">
-        <v>6239538</v>
+        <v>6239439</v>
       </c>
       <c r="S6" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,19 +1256,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,19 +1273,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123445749</v>
+        <v>123445753</v>
       </c>
       <c r="B7" t="n">
         <v>57642</v>
@@ -1347,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410567</v>
+        <v>410586</v>
       </c>
       <c r="R7" t="n">
-        <v>6239439</v>
+        <v>6239506</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1533,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123429666</v>
+        <v>123445750</v>
       </c>
       <c r="B9" t="n">
-        <v>57861</v>
+        <v>57642</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1545,20 +1539,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1571,27 +1565,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410584</v>
+        <v>410535</v>
       </c>
       <c r="R9" t="n">
-        <v>6239531</v>
+        <v>6239462</v>
       </c>
       <c r="S9" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1618,19 +1616,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,22 +1633,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123445750</v>
+        <v>123432412</v>
       </c>
       <c r="B10" t="n">
-        <v>57642</v>
+        <v>57861</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1669,20 +1657,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1692,34 +1680,30 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410535</v>
+        <v>410583</v>
       </c>
       <c r="R10" t="n">
-        <v>6239462</v>
+        <v>6239538</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1746,9 +1730,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,22 +1757,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123445753</v>
+        <v>123429666</v>
       </c>
       <c r="B11" t="n">
-        <v>57642</v>
+        <v>57861</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1787,20 +1781,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1813,31 +1807,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410586</v>
+        <v>410584</v>
       </c>
       <c r="R11" t="n">
-        <v>6239506</v>
+        <v>6239531</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1864,9 +1854,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,12 +1881,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123445749</v>
+        <v>123445753</v>
       </c>
       <c r="B6" t="n">
         <v>57642</v>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410567</v>
+        <v>410586</v>
       </c>
       <c r="R6" t="n">
-        <v>6239439</v>
+        <v>6239506</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1285,7 +1285,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123445753</v>
+        <v>123445750</v>
       </c>
       <c r="B7" t="n">
         <v>57642</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410586</v>
+        <v>410535</v>
       </c>
       <c r="R7" t="n">
-        <v>6239506</v>
+        <v>6239462</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1403,7 +1403,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123432410</v>
+        <v>123445749</v>
       </c>
       <c r="B8" t="n">
         <v>57642</v>
@@ -1441,27 +1441,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410583</v>
+        <v>410567</v>
       </c>
       <c r="R8" t="n">
-        <v>6239538</v>
+        <v>6239439</v>
       </c>
       <c r="S8" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1488,19 +1492,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,19 +1509,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123445750</v>
+        <v>123432410</v>
       </c>
       <c r="B9" t="n">
         <v>57642</v>
@@ -1565,31 +1559,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410535</v>
+        <v>410583</v>
       </c>
       <c r="R9" t="n">
-        <v>6239462</v>
+        <v>6239538</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1616,9 +1606,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,12 +1633,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -1167,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123445753</v>
+        <v>123429666</v>
       </c>
       <c r="B6" t="n">
-        <v>57642</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,20 +1179,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1205,31 +1205,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410586</v>
+        <v>410584</v>
       </c>
       <c r="R6" t="n">
-        <v>6239506</v>
+        <v>6239531</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,9 +1252,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,12 +1279,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1403,7 +1409,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123445749</v>
+        <v>123445753</v>
       </c>
       <c r="B8" t="n">
         <v>57642</v>
@@ -1459,10 +1465,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410567</v>
+        <v>410586</v>
       </c>
       <c r="R8" t="n">
-        <v>6239439</v>
+        <v>6239506</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1521,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123432410</v>
+        <v>123432412</v>
       </c>
       <c r="B9" t="n">
-        <v>57642</v>
+        <v>57861</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,20 +1539,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1556,14 +1562,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1608,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1618,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,10 +1651,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123432412</v>
+        <v>123445749</v>
       </c>
       <c r="B10" t="n">
-        <v>57861</v>
+        <v>57642</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1657,20 +1663,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1680,30 +1686,34 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410583</v>
+        <v>410567</v>
       </c>
       <c r="R10" t="n">
-        <v>6239538</v>
+        <v>6239439</v>
       </c>
       <c r="S10" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1730,19 +1740,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,22 +1757,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123429666</v>
+        <v>123432410</v>
       </c>
       <c r="B11" t="n">
-        <v>57861</v>
+        <v>57642</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1781,20 +1781,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1811,7 +1811,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1821,13 +1821,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410584</v>
+        <v>410583</v>
       </c>
       <c r="R11" t="n">
-        <v>6239531</v>
+        <v>6239538</v>
       </c>
       <c r="S11" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1891,6 +1891,121 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133615668</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skåneleden, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>410578</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6239529</v>
+      </c>
+      <c r="S12" t="n">
+        <v>79</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123091145</v>
+        <v>123091142</v>
       </c>
       <c r="B2" t="n">
-        <v>57642</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +712,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -799,32 +794,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123091142</v>
+        <v>123091148</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,7 +824,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -923,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123091148</v>
+        <v>123429666</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -958,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -975,13 +960,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410558</v>
+        <v>410584</v>
       </c>
       <c r="R4" t="n">
-        <v>6239578</v>
+        <v>6239531</v>
       </c>
       <c r="S4" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,22 +990,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,15 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123091150</v>
+        <v>123432412</v>
       </c>
       <c r="B5" t="n">
-        <v>58169</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,16 +1043,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1082,12 +1062,16 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1095,13 +1079,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410558</v>
+        <v>410583</v>
       </c>
       <c r="R5" t="n">
-        <v>6239578</v>
+        <v>6239538</v>
       </c>
       <c r="S5" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,15 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123445753</v>
+        <v>123091145</v>
       </c>
       <c r="B6" t="n">
-        <v>57664</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,11 +1184,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
@@ -1219,17 +1194,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410586</v>
+        <v>410558</v>
       </c>
       <c r="R6" t="n">
-        <v>6239506</v>
+        <v>6239578</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1253,12 +1228,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,27 +1258,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123445750</v>
+        <v>123432410</v>
       </c>
       <c r="B7" t="n">
-        <v>57664</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,31 +1303,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fäje myr norr, Sk</t>
+          <t>Skåneleden, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410535</v>
+        <v>410583</v>
       </c>
       <c r="R7" t="n">
-        <v>6239462</v>
+        <v>6239538</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1374,9 +1350,19 @@
           <t>2025-03-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,44 +1377,39 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Arnström</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123429666</v>
+        <v>123445749</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1441,27 +1422,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410584</v>
+        <v>410567</v>
       </c>
       <c r="R8" t="n">
-        <v>6239531</v>
+        <v>6239439</v>
       </c>
       <c r="S8" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1488,19 +1473,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,44 +1490,39 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123432412</v>
+        <v>123445750</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1562,30 +1532,34 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skåneleden, Sk</t>
+          <t>Fäje myr norr, Sk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410583</v>
+        <v>410535</v>
       </c>
       <c r="R9" t="n">
-        <v>6239538</v>
+        <v>6239462</v>
       </c>
       <c r="S9" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1612,19 +1586,9 @@
           <t>2025-03-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,27 +1603,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Thomas Arnström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123445749</v>
+        <v>123445753</v>
       </c>
       <c r="B10" t="n">
-        <v>57664</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410567</v>
+        <v>410586</v>
       </c>
       <c r="R10" t="n">
-        <v>6239439</v>
+        <v>6239506</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1769,32 +1728,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123432410</v>
+        <v>133471829</v>
       </c>
       <c r="B11" t="n">
-        <v>57664</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>103023</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1809,11 +1763,7 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1821,13 +1771,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410583</v>
+        <v>410584</v>
       </c>
       <c r="R11" t="n">
-        <v>6239538</v>
+        <v>6239531</v>
       </c>
       <c r="S11" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1851,22 +1801,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,27 +1843,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133615668</v>
+        <v>123091150</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>58636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1923,7 +1873,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1936,13 +1886,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410578</v>
+        <v>410558</v>
       </c>
       <c r="R12" t="n">
-        <v>6239529</v>
+        <v>6239578</v>
       </c>
       <c r="S12" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1966,22 +1916,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 4598-2025 artfynd.xlsx
+++ b/artfynd/A 4598-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123091142</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123091148</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123429666</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123432412</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123091145</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1386,6 +1416,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123432410</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1499,6 +1534,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123445749</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1612,6 +1652,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123445750</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1725,6 +1770,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123445753</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1840,6 +1890,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133471829</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1955,8 +2010,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123091150</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>